--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3310,9 +3310,14 @@
       <c r="E84" s="9" t="n">
         <v>46278.8125</v>
       </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F84" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1078845134897367</t>
         </is>
       </c>
       <c r="I84" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2603,9 +2603,14 @@
       <c r="E61" s="7" t="n">
         <v>46278.96875</v>
       </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1842448173969668</t>
         </is>
       </c>
       <c r="I61" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2637,9 +2637,14 @@
       <c r="E62" s="7" t="n">
         <v>46279.11458333334</v>
       </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F62" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1384895266647320</t>
         </is>
       </c>
       <c r="I62" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2671,9 +2671,14 @@
       <c r="E63" s="7" t="n">
         <v>46279.26041666666</v>
       </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1580122724127623</t>
         </is>
       </c>
       <c r="I63" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2705,9 +2705,14 @@
       <c r="E64" s="7" t="n">
         <v>46279.96875</v>
       </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F64" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2303412473791078</t>
         </is>
       </c>
       <c r="I64" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2739,9 +2739,14 @@
       <c r="E65" s="7" t="n">
         <v>46280.11458333334</v>
       </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F65" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1094925179678434</t>
         </is>
       </c>
       <c r="I65" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2773,9 +2773,14 @@
       <c r="E66" s="7" t="n">
         <v>46280.26041666666</v>
       </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F66" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1596641515344102</t>
         </is>
       </c>
       <c r="I66" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2807,9 +2807,14 @@
       <c r="E67" s="7" t="n">
         <v>46280.96875</v>
       </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F67" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1089459303615057</t>
         </is>
       </c>
       <c r="I67" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2841,9 +2841,14 @@
       <c r="E68" s="7" t="n">
         <v>46281.11458333334</v>
       </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F68" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1554692825981855</t>
         </is>
       </c>
       <c r="I68" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2875,9 +2875,14 @@
       <c r="E69" s="7" t="n">
         <v>46281.26041666666</v>
       </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F69" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1738583853863035</t>
         </is>
       </c>
       <c r="I69" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2909,9 +2909,14 @@
       <c r="E70" s="7" t="n">
         <v>46281.96875</v>
       </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F70" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>28378486475112311</t>
         </is>
       </c>
       <c r="I70" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2943,9 +2943,14 @@
       <c r="E71" s="7" t="n">
         <v>46282.11458333334</v>
       </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F71" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1802869644400180</t>
         </is>
       </c>
       <c r="I71" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2977,9 +2977,14 @@
       <c r="E72" s="7" t="n">
         <v>46282.26041666666</v>
       </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F72" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1417575107233502</t>
         </is>
       </c>
       <c r="I72" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3011,9 +3011,14 @@
       <c r="E73" s="7" t="n">
         <v>46282.96875</v>
       </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F73" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1598127381722728</t>
         </is>
       </c>
       <c r="I73" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3045,9 +3045,14 @@
       <c r="E74" s="7" t="n">
         <v>46283.11458333334</v>
       </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F74" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>859951793777786</t>
         </is>
       </c>
       <c r="I74" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3079,9 +3079,14 @@
       <c r="E75" s="7" t="n">
         <v>46283.26041666666</v>
       </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F75" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2337675443436436</t>
         </is>
       </c>
       <c r="I75" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -769,9 +769,14 @@
       <c r="E5" s="7" t="n">
         <v>46283.98958333334</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1399266798369651</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -803,9 +803,14 @@
       <c r="E6" s="7" t="n">
         <v>46284.09375</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1099671139421916</t>
         </is>
       </c>
       <c r="I6" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -837,9 +837,14 @@
       <c r="E7" s="7" t="n">
         <v>46284.26041666666</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1573768917559985</t>
         </is>
       </c>
       <c r="I7" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -871,9 +871,14 @@
       <c r="E8" s="7" t="n">
         <v>46284.96875</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2425632444626768</t>
         </is>
       </c>
       <c r="I8" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -905,9 +905,14 @@
       <c r="E9" s="7" t="n">
         <v>46285.11458333334</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2342205279851642</t>
         </is>
       </c>
       <c r="I9" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1138,9 +1138,14 @@
       <c r="E16" s="7" t="n">
         <v>46285.26041666666</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1127698786865132</t>
         </is>
       </c>
       <c r="I16" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1172,9 +1172,14 @@
       <c r="E17" s="7" t="n">
         <v>46285.96875</v>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1436750421726937</t>
         </is>
       </c>
       <c r="I17" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1206,9 +1206,14 @@
       <c r="E18" s="7" t="n">
         <v>46286.11458333334</v>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2255769375212231</t>
         </is>
       </c>
       <c r="I18" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1240,9 +1240,14 @@
       <c r="E19" s="7" t="n">
         <v>46286.26041666666</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1639648941277110</t>
         </is>
       </c>
       <c r="I19" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1274,9 +1274,14 @@
       <c r="E20" s="7" t="n">
         <v>46286.96875</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>949777544262991</t>
         </is>
       </c>
       <c r="I20" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1308,9 +1308,14 @@
       <c r="E21" s="7" t="n">
         <v>46287.11458333334</v>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1106622068375289</t>
         </is>
       </c>
       <c r="I21" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1342,9 +1342,14 @@
       <c r="E22" s="7" t="n">
         <v>46287.26041666666</v>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>4579077625661074</t>
         </is>
       </c>
       <c r="I22" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1376,9 +1376,14 @@
       <c r="E23" s="7" t="n">
         <v>46287.96875</v>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2888294648195633</t>
         </is>
       </c>
       <c r="I23" s="5" t="n"/>
